--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,87 +448,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-227422117.42</v>
+        <v>-233848356.7500001</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-231320501.7500001</v>
+        <v>-233848356.7500001</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3898384.33</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-232695501.7500001</v>
+        <v>-241526192.8500001</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1375000</v>
+        <v>7677836.1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-233848356.7500001</v>
+        <v>-247087527.33</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1152855</v>
+        <v>5561334.48</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-233848356.7500001</v>
+        <v>-247087527.33</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -543,11 +543,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-233848356.7500001</v>
+        <v>-247087527.33</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -562,11 +562,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-233848356.7500001</v>
+        <v>-247087527.33</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -581,49 +581,49 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-241526192.8500001</v>
+        <v>-247087527.33</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>7677836.1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-247087527.33</v>
+        <v>-252087527.33</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>5561334.48</v>
+        <v>5000000</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-247087527.33</v>
+        <v>-252087527.33</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -638,30 +638,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-247087527.33</v>
+        <v>-255336967.2900001</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>3249439.96</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-247087527.33</v>
+        <v>-255336967.2900001</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -676,49 +676,49 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-247087527.33</v>
+        <v>-258619226.3500001</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3282259.06</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-252087527.33</v>
+        <v>-258619226.3500001</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-252087527.33</v>
+        <v>-258619226.3500001</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -733,17 +733,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-255336967.2900001</v>
+        <v>-263619226.3500001</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>3249439.96</v>
+        <v>5000000</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -752,11 +752,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-255336967.2900001</v>
+        <v>-263619226.3500001</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -771,49 +771,49 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-258619226.3500001</v>
+        <v>-287830293.5000001</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3282259.06</v>
+        <v>24211067.15</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-258619226.3500001</v>
+        <v>-288640293.5000001</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>810000</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-258619226.3500001</v>
+        <v>-288640293.5000001</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -828,11 +828,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-263619226.3500001</v>
+        <v>-293640293.5000001</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -847,11 +847,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-263619226.3500001</v>
+        <v>-293640293.5000001</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -866,87 +866,87 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-287830293.5000001</v>
+        <v>-453516985.8600001</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>24211067.15</v>
+        <v>159876692.36</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-288640293.5000001</v>
+        <v>-453516985.8600001</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>810000</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-288640293.5000001</v>
+        <v>-458616985.8600001</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>5100000</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-293640293.5000001</v>
+        <v>-464756985.8600001</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>5000000</v>
+        <v>6140000</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-293640293.5000001</v>
+        <v>-464756985.8600001</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -961,30 +961,30 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-453516985.8600001</v>
+        <v>-471131985.8600001</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>159876692.36</v>
+        <v>6375000</v>
       </c>
       <c r="E29" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-453516985.8600001</v>
+        <v>-471131985.8600001</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -999,17 +999,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-458616985.8600001</v>
+        <v>-476131985.8600001</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>5100000</v>
+        <v>5000000</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -1018,20 +1018,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-464756985.8600001</v>
+        <v>-476131985.8600001</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>6140000</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -467,45 +467,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-233848356.7500001</v>
+        <v>-241526192.8500001</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>7677836.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-241526192.8500001</v>
+        <v>-247087527.33</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>7677836.1</v>
+        <v>5561334.48</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -515,16 +515,16 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>5561334.48</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -543,7 +543,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -562,7 +562,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -581,26 +581,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-247087527.33</v>
+        <v>-252087527.33</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -610,35 +610,35 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-252087527.33</v>
+        <v>-255336967.2900001</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3249439.96</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -648,35 +648,35 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>3249439.96</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-255336967.2900001</v>
+        <v>-258619226.3500001</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3282259.06</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -686,16 +686,16 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3282259.06</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -714,26 +714,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-258619226.3500001</v>
+        <v>-263619226.3500001</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -743,54 +743,54 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-263619226.3500001</v>
+        <v>-287830293.5000001</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>24211067.15</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-287830293.5000001</v>
+        <v>-288640293.5000001</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>24211067.15</v>
+        <v>810000</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -800,35 +800,35 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>810000</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-288640293.5000001</v>
+        <v>-293640293.5000001</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -838,35 +838,35 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-293640293.5000001</v>
+        <v>-453516985.8600001</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>159876692.36</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -876,54 +876,54 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>159876692.36</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-453516985.8600001</v>
+        <v>-458616985.8600001</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>5100000</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-458616985.8600001</v>
+        <v>-464756985.8600001</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>5100000</v>
+        <v>6140000</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -933,35 +933,35 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>6140000</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-464756985.8600001</v>
+        <v>-471131985.8600001</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>6375000</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -971,35 +971,35 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>6375000</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-471131985.8600001</v>
+        <v>-476131985.8600001</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1009,16 +1009,16 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B32" t="n">

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,26 +448,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-21758574.34</v>
+        <v>-52909119.14</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>31150544.8</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -477,54 +477,54 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>31150544.8</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-52909119.14</v>
+        <v>-57909119.14</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-57909119.14</v>
+        <v>-222377897.27</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>5000000</v>
+        <v>164468778.13</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -534,16 +534,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>164468778.13</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -562,26 +562,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-222377897.27</v>
+        <v>-224288209.17</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1910311.9</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -591,54 +591,54 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1910311.9</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-224288209.17</v>
+        <v>-225663209.17</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1375000</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-225663209.17</v>
+        <v>-231875534.19</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1375000</v>
+        <v>6212325.02</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -648,16 +648,16 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>6212325.02</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -676,7 +676,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -695,7 +695,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -714,7 +714,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -733,7 +733,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -752,7 +752,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -771,26 +771,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-231875534.19</v>
+        <v>-233829708.89</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1954174.7</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -800,16 +800,16 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1954174.7</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -828,7 +828,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -847,26 +847,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-233829708.89</v>
+        <v>-238829708.89</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -876,54 +876,54 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-238829708.89</v>
+        <v>-291279569.25</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>52449860.36</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-291279569.25</v>
+        <v>-296279569.25</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>52449860.36</v>
+        <v>5000000</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -933,16 +933,16 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -961,7 +961,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -980,7 +980,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -999,7 +999,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1018,20 +1018,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-296279569.25</v>
+        <v>-301279569.25</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
